--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/26.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/26.xlsx
@@ -426,13 +426,13 @@
         <v>-21.46274266857845</v>
       </c>
       <c r="E2">
-        <v>-10.68090615593898</v>
+        <v>-10.33139400355298</v>
       </c>
       <c r="F2">
-        <v>-1.508411638278081</v>
+        <v>-2.185919445197162</v>
       </c>
       <c r="G2">
-        <v>-12.44933413546195</v>
+        <v>-11.62842477917995</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.80326060489736</v>
       </c>
       <c r="E3">
-        <v>-10.79593392420782</v>
+        <v>-10.68780302185267</v>
       </c>
       <c r="F3">
-        <v>-1.265841738033883</v>
+        <v>-1.934868799775785</v>
       </c>
       <c r="G3">
-        <v>-12.27901318855752</v>
+        <v>-11.64702342401957</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.01763397135269</v>
       </c>
       <c r="E4">
-        <v>-12.50692725852591</v>
+        <v>-11.47149620514609</v>
       </c>
       <c r="F4">
-        <v>-1.731536797292514</v>
+        <v>-2.345269558849806</v>
       </c>
       <c r="G4">
-        <v>-11.40548271092881</v>
+        <v>-10.6367541734368</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.20814916247185</v>
       </c>
       <c r="E5">
-        <v>-12.72097463944646</v>
+        <v>-13.22609874415805</v>
       </c>
       <c r="F5">
-        <v>-1.251628769295772</v>
+        <v>-2.475832650077507</v>
       </c>
       <c r="G5">
-        <v>-11.09672799175422</v>
+        <v>-11.02988807731634</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.39730551390857</v>
       </c>
       <c r="E6">
-        <v>-13.8395394186591</v>
+        <v>-14.77263148793957</v>
       </c>
       <c r="F6">
-        <v>-1.355379719375083</v>
+        <v>-2.003193040379673</v>
       </c>
       <c r="G6">
-        <v>-10.62751113029116</v>
+        <v>-10.62885190123456</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.61041223131495</v>
       </c>
       <c r="E7">
-        <v>-13.41090576841107</v>
+        <v>-13.8632142807712</v>
       </c>
       <c r="F7">
-        <v>-1.344738799329245</v>
+        <v>-2.25633417760943</v>
       </c>
       <c r="G7">
-        <v>-10.00330445831604</v>
+        <v>-10.55189495962867</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.86758374854342</v>
       </c>
       <c r="E8">
-        <v>-15.07900992540252</v>
+        <v>-15.48320792990515</v>
       </c>
       <c r="F8">
-        <v>-1.330904336304924</v>
+        <v>-2.004132177987529</v>
       </c>
       <c r="G8">
-        <v>-10.72292436327849</v>
+        <v>-9.373304331647191</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.19012297782598</v>
       </c>
       <c r="E9">
-        <v>-16.1401581826719</v>
+        <v>-16.39808647672678</v>
       </c>
       <c r="F9">
-        <v>-1.100415736636656</v>
+        <v>-1.861617650068964</v>
       </c>
       <c r="G9">
-        <v>-9.56336606160229</v>
+        <v>-9.263817969572415</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.56888288745327</v>
       </c>
       <c r="E10">
-        <v>-15.35862508148013</v>
+        <v>-17.17701570536413</v>
       </c>
       <c r="F10">
-        <v>-1.127427424730391</v>
+        <v>-2.330041434619897</v>
       </c>
       <c r="G10">
-        <v>-9.080152213599188</v>
+        <v>-9.230282143259597</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.00878210835581</v>
       </c>
       <c r="E11">
-        <v>-17.55750714843661</v>
+        <v>-16.64066777236966</v>
       </c>
       <c r="F11">
-        <v>-0.9361125827334746</v>
+        <v>-1.942668551409324</v>
       </c>
       <c r="G11">
-        <v>-8.555761800178633</v>
+        <v>-8.751196545543968</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.49357868682284</v>
       </c>
       <c r="E12">
-        <v>-17.52418210821417</v>
+        <v>-15.87465828007619</v>
       </c>
       <c r="F12">
-        <v>-1.212681481570327</v>
+        <v>-1.715150192185462</v>
       </c>
       <c r="G12">
-        <v>-8.560237657747727</v>
+        <v>-7.30357774485916</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.9860006573683</v>
       </c>
       <c r="E13">
-        <v>-18.84168727905777</v>
+        <v>-18.53325291439534</v>
       </c>
       <c r="F13">
-        <v>-1.143727717865051</v>
+        <v>-2.116857197636678</v>
       </c>
       <c r="G13">
-        <v>-6.898873484319875</v>
+        <v>-7.194687280981451</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.46907735032907</v>
       </c>
       <c r="E14">
-        <v>-20.40195035603055</v>
+        <v>-20.01454393314836</v>
       </c>
       <c r="F14">
-        <v>-0.7967060776739595</v>
+        <v>-1.634494425471005</v>
       </c>
       <c r="G14">
-        <v>-6.94009308682934</v>
+        <v>-7.682386918190265</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.91633501595888</v>
       </c>
       <c r="E15">
-        <v>-20.21068572784258</v>
+        <v>-20.76102664552075</v>
       </c>
       <c r="F15">
-        <v>-0.4848221206287229</v>
+        <v>-1.540229081972218</v>
       </c>
       <c r="G15">
-        <v>-6.142096016224638</v>
+        <v>-6.581259745282197</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.30687559669451</v>
       </c>
       <c r="E16">
-        <v>-21.45238424379778</v>
+        <v>-22.70608774434731</v>
       </c>
       <c r="F16">
-        <v>-0.3783392778452784</v>
+        <v>-1.453276500537972</v>
       </c>
       <c r="G16">
-        <v>-5.931614841383316</v>
+        <v>-6.906401664876177</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.64631057584109</v>
       </c>
       <c r="E17">
-        <v>-21.57976116068553</v>
+        <v>-21.70838340792539</v>
       </c>
       <c r="F17">
-        <v>-0.5770983294977177</v>
+        <v>-1.236958109548098</v>
       </c>
       <c r="G17">
-        <v>-5.231609918741041</v>
+        <v>-4.882423506895334</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.93705689111091</v>
       </c>
       <c r="E18">
-        <v>-22.61596205464665</v>
+        <v>-23.13952610551747</v>
       </c>
       <c r="F18">
-        <v>-0.1394689146195466</v>
+        <v>-1.011249134332626</v>
       </c>
       <c r="G18">
-        <v>-5.397805925903533</v>
+        <v>-4.420450119072197</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.1925572109495</v>
       </c>
       <c r="E19">
-        <v>-23.88819154236156</v>
+        <v>-23.15362324510335</v>
       </c>
       <c r="F19">
-        <v>-0.01525410855388441</v>
+        <v>-0.6768860555236418</v>
       </c>
       <c r="G19">
-        <v>-4.59849787926528</v>
+        <v>-4.601335016792436</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.43924067843396</v>
       </c>
       <c r="E20">
-        <v>-24.9526772849746</v>
+        <v>-24.71946087357957</v>
       </c>
       <c r="F20">
-        <v>0.3651370071284742</v>
+        <v>-0.535134082003361</v>
       </c>
       <c r="G20">
-        <v>-4.435122456902246</v>
+        <v>-4.459008042968089</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.693493572802169</v>
       </c>
       <c r="E21">
-        <v>-25.37595827894555</v>
+        <v>-25.67251898475987</v>
       </c>
       <c r="F21">
-        <v>0.4406433540588807</v>
+        <v>-0.4729015662032101</v>
       </c>
       <c r="G21">
-        <v>-4.43601630419785</v>
+        <v>-4.198107259563665</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.983127038513785</v>
       </c>
       <c r="E22">
-        <v>-25.75875924376194</v>
+        <v>-26.56433854193444</v>
       </c>
       <c r="F22">
-        <v>0.7590086275630533</v>
+        <v>-0.5915971571535659</v>
       </c>
       <c r="G22">
-        <v>-3.857342875569864</v>
+        <v>-3.828286217371681</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.337480087723886</v>
       </c>
       <c r="E23">
-        <v>-26.1382951788188</v>
+        <v>-27.0566968784184</v>
       </c>
       <c r="F23">
-        <v>0.9212149548341925</v>
+        <v>-0.346861539070004</v>
       </c>
       <c r="G23">
-        <v>-4.150289739794433</v>
+        <v>-3.677053876046695</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.772468695545219</v>
       </c>
       <c r="E24">
-        <v>-27.73988058111158</v>
+        <v>-26.50146973728595</v>
       </c>
       <c r="F24">
-        <v>1.188381391651081</v>
+        <v>-0.07347984838797342</v>
       </c>
       <c r="G24">
-        <v>-4.467387033727984</v>
+        <v>-3.558205291186859</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.310999033320124</v>
       </c>
       <c r="E25">
-        <v>-27.21851736860849</v>
+        <v>-26.67683489323299</v>
       </c>
       <c r="F25">
-        <v>0.9866600180838122</v>
+        <v>-0.2335434215555229</v>
       </c>
       <c r="G25">
-        <v>-3.545962893782634</v>
+        <v>-3.779521881578217</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.96297887854078</v>
       </c>
       <c r="E26">
-        <v>-27.15630519269112</v>
+        <v>-27.83267354200276</v>
       </c>
       <c r="F26">
-        <v>1.02355719850172</v>
+        <v>0.08111914751835228</v>
       </c>
       <c r="G26">
-        <v>-4.166918610038191</v>
+        <v>-3.326377718708316</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.719783062235706</v>
       </c>
       <c r="E27">
-        <v>-27.85843150215838</v>
+        <v>-25.47914408768433</v>
       </c>
       <c r="F27">
-        <v>0.9420992847410924</v>
+        <v>0.6597261037241544</v>
       </c>
       <c r="G27">
-        <v>-3.854787134413547</v>
+        <v>-3.917972206576077</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.577658215235689</v>
       </c>
       <c r="E28">
-        <v>-26.46084479696314</v>
+        <v>-27.567735170184</v>
       </c>
       <c r="F28">
-        <v>1.048161653603988</v>
+        <v>-0.07463753741215964</v>
       </c>
       <c r="G28">
-        <v>-3.512066218006037</v>
+        <v>-3.957364387947865</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.518231777311831</v>
       </c>
       <c r="E29">
-        <v>-27.29921024695117</v>
+        <v>-27.68642647392504</v>
       </c>
       <c r="F29">
-        <v>0.9602533056497748</v>
+        <v>-0.3739832947248622</v>
       </c>
       <c r="G29">
-        <v>-4.062672841552081</v>
+        <v>-3.537540865930728</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.519857205271034</v>
       </c>
       <c r="E30">
-        <v>-26.63669902810301</v>
+        <v>-26.51665823910768</v>
       </c>
       <c r="F30">
-        <v>1.088799547394164</v>
+        <v>0.146216587319533</v>
       </c>
       <c r="G30">
-        <v>-4.256190781050178</v>
+        <v>-3.707153356089748</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.570300094925835</v>
       </c>
       <c r="E31">
-        <v>-27.18668672480858</v>
+        <v>-26.39691180092285</v>
       </c>
       <c r="F31">
-        <v>1.078926724717314</v>
+        <v>0.07552074710727384</v>
       </c>
       <c r="G31">
-        <v>-3.817583223643217</v>
+        <v>-4.221923324173183</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.649896505904359</v>
       </c>
       <c r="E32">
-        <v>-26.4219723760813</v>
+        <v>-26.62246150582289</v>
       </c>
       <c r="F32">
-        <v>1.029876185104324</v>
+        <v>0.1105436115742595</v>
       </c>
       <c r="G32">
-        <v>-4.437264379866155</v>
+        <v>-3.604923709837054</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.745261707334521</v>
       </c>
       <c r="E33">
-        <v>-25.76435190916142</v>
+        <v>-25.54921769447902</v>
       </c>
       <c r="F33">
-        <v>0.784504709095713</v>
+        <v>-0.05756756320259557</v>
       </c>
       <c r="G33">
-        <v>-3.960754386580078</v>
+        <v>-3.515045708991381</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.848344714125104</v>
       </c>
       <c r="E34">
-        <v>-25.41229022590909</v>
+        <v>-26.2916157232965</v>
       </c>
       <c r="F34">
-        <v>0.8840342910574205</v>
+        <v>-0.0312843798299625</v>
       </c>
       <c r="G34">
-        <v>-4.278344951798982</v>
+        <v>-3.841488672982295</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.945484047422402</v>
       </c>
       <c r="E35">
-        <v>-25.69563231609502</v>
+        <v>-25.01104931493347</v>
       </c>
       <c r="F35">
-        <v>0.6875834907767343</v>
+        <v>-0.1413107645992027</v>
       </c>
       <c r="G35">
-        <v>-3.363886199668258</v>
+        <v>-3.367991276136955</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.034099044707332</v>
       </c>
       <c r="E36">
-        <v>-24.7389604826566</v>
+        <v>-25.13244411765709</v>
       </c>
       <c r="F36">
-        <v>0.931714925053556</v>
+        <v>-0.243315678906742</v>
       </c>
       <c r="G36">
-        <v>-3.792356866633971</v>
+        <v>-4.037254472901557</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.112762369019887</v>
       </c>
       <c r="E37">
-        <v>-24.48005856669007</v>
+        <v>-24.70957521482083</v>
       </c>
       <c r="F37">
-        <v>0.8175709049041733</v>
+        <v>-0.04816747674150473</v>
       </c>
       <c r="G37">
-        <v>-3.061030872644652</v>
+        <v>-3.630633406495034</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.177688489985385</v>
       </c>
       <c r="E38">
-        <v>-23.92863987219808</v>
+        <v>-25.13572726131265</v>
       </c>
       <c r="F38">
-        <v>0.9537537765728114</v>
+        <v>0.03173207039833083</v>
       </c>
       <c r="G38">
-        <v>-3.660322378891218</v>
+        <v>-3.575267842896263</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.237625681573739</v>
       </c>
       <c r="E39">
-        <v>-22.9948368324984</v>
+        <v>-23.5941984813096</v>
       </c>
       <c r="F39">
-        <v>0.657306201085363</v>
+        <v>-0.3365112290596495</v>
       </c>
       <c r="G39">
-        <v>-3.401268879897708</v>
+        <v>-3.105004849042791</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.299419352747379</v>
       </c>
       <c r="E40">
-        <v>-23.01626104302868</v>
+        <v>-24.06425408330578</v>
       </c>
       <c r="F40">
-        <v>0.6826154053200008</v>
+        <v>-0.1660720065870984</v>
       </c>
       <c r="G40">
-        <v>-3.449735266592639</v>
+        <v>-3.505594101476762</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.369968299817843</v>
       </c>
       <c r="E41">
-        <v>-23.3443489848844</v>
+        <v>-22.35157162818283</v>
       </c>
       <c r="F41">
-        <v>0.6084267017112398</v>
+        <v>0.03578794124777126</v>
       </c>
       <c r="G41">
-        <v>-3.477050577837165</v>
+        <v>-2.431620023081796</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.467774018185143</v>
       </c>
       <c r="E42">
-        <v>-21.036883168172</v>
+        <v>-23.02782676564427</v>
       </c>
       <c r="F42">
-        <v>0.6526770286945334</v>
+        <v>0.304411387506864</v>
       </c>
       <c r="G42">
-        <v>-2.609823378915225</v>
+        <v>-2.677424718827142</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.603217636860582</v>
       </c>
       <c r="E43">
-        <v>-21.48240349799463</v>
+        <v>-21.91015409581115</v>
       </c>
       <c r="F43">
-        <v>0.6891925359868207</v>
+        <v>-0.2114459729173963</v>
       </c>
       <c r="G43">
-        <v>-2.985712651080693</v>
+        <v>-2.988817942796529</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.788091663116182</v>
       </c>
       <c r="E44">
-        <v>-19.69014216913488</v>
+        <v>-21.52543758648952</v>
       </c>
       <c r="F44">
-        <v>0.8640542572282365</v>
+        <v>0.02040619754406563</v>
       </c>
       <c r="G44">
-        <v>-3.437880203016509</v>
+        <v>-2.816606674389181</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.038700260349676</v>
       </c>
       <c r="E45">
-        <v>-20.35622182550109</v>
+        <v>-20.30082500296526</v>
       </c>
       <c r="F45">
-        <v>0.7034078802838052</v>
+        <v>0.01047794516017573</v>
       </c>
       <c r="G45">
-        <v>-3.233722170155194</v>
+        <v>-3.751468318678433</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.358474105455039</v>
       </c>
       <c r="E46">
-        <v>-20.24216767914391</v>
+        <v>-20.09738783664468</v>
       </c>
       <c r="F46">
-        <v>0.3616275148198604</v>
+        <v>-0.45079144791776</v>
       </c>
       <c r="G46">
-        <v>-3.357126065677067</v>
+        <v>-3.749011893888293</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.753858340118915</v>
       </c>
       <c r="E47">
-        <v>-18.83063327400504</v>
+        <v>-19.85673567092906</v>
       </c>
       <c r="F47">
-        <v>0.694022839028911</v>
+        <v>-0.3777469718329041</v>
       </c>
       <c r="G47">
-        <v>-3.511804684908434</v>
+        <v>-3.248778531267799</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.226760455352141</v>
       </c>
       <c r="E48">
-        <v>-18.9832790758556</v>
+        <v>-19.30370031121632</v>
       </c>
       <c r="F48">
-        <v>0.7957870300373037</v>
+        <v>-0.1766400761608259</v>
       </c>
       <c r="G48">
-        <v>-3.226488628151886</v>
+        <v>-2.767160366214627</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.762437814917028</v>
       </c>
       <c r="E49">
-        <v>-17.96130211875256</v>
+        <v>-19.08334476600309</v>
       </c>
       <c r="F49">
-        <v>0.8287597871967529</v>
+        <v>-0.03414376086028842</v>
       </c>
       <c r="G49">
-        <v>-3.608611657567802</v>
+        <v>-4.038115214741768</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.355174286902029</v>
       </c>
       <c r="E50">
-        <v>-17.65216584061895</v>
+        <v>-16.91099502825755</v>
       </c>
       <c r="F50">
-        <v>0.7108718862632714</v>
+        <v>0.06947257421621059</v>
       </c>
       <c r="G50">
-        <v>-3.202073354799761</v>
+        <v>-4.623780515548694</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.990940285675418</v>
       </c>
       <c r="E51">
-        <v>-16.7163748008299</v>
+        <v>-17.43006683291275</v>
       </c>
       <c r="F51">
-        <v>0.5135049121105034</v>
+        <v>0.154483532198127</v>
       </c>
       <c r="G51">
-        <v>-3.85786263121953</v>
+        <v>-4.075206566963762</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.64546052248189</v>
       </c>
       <c r="E52">
-        <v>-15.71787798145664</v>
+        <v>-17.15331367240799</v>
       </c>
       <c r="F52">
-        <v>0.349731507836037</v>
+        <v>0.06336422050036064</v>
       </c>
       <c r="G52">
-        <v>-3.619950276039806</v>
+        <v>-3.910165940194475</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.30877540642407</v>
       </c>
       <c r="E53">
-        <v>-16.59773783877695</v>
+        <v>-17.71449575686052</v>
       </c>
       <c r="F53">
-        <v>0.5978079535482184</v>
+        <v>-0.169065210767279</v>
       </c>
       <c r="G53">
-        <v>-4.063368056115328</v>
+        <v>-3.397839154719024</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.96026221864013</v>
       </c>
       <c r="E54">
-        <v>-15.14897484882103</v>
+        <v>-14.91504293853279</v>
       </c>
       <c r="F54">
-        <v>0.5044928335986952</v>
+        <v>-0.3491262385290824</v>
       </c>
       <c r="G54">
-        <v>-3.987116260709295</v>
+        <v>-4.379978699854607</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.57777288323331</v>
       </c>
       <c r="E55">
-        <v>-15.00923519789233</v>
+        <v>-15.1481325526556</v>
       </c>
       <c r="F55">
-        <v>0.5020966865486354</v>
+        <v>-0.2317902591071315</v>
       </c>
       <c r="G55">
-        <v>-3.923335290349696</v>
+        <v>-4.264775025633509</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.15443018246243</v>
       </c>
       <c r="E56">
-        <v>-14.49284424984967</v>
+        <v>-16.12403228673059</v>
       </c>
       <c r="F56">
-        <v>0.3571939301095877</v>
+        <v>-0.3567042713344601</v>
       </c>
       <c r="G56">
-        <v>-4.242074614870726</v>
+        <v>-4.95121333265585</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.67500060308034</v>
       </c>
       <c r="E57">
-        <v>-14.43261101707365</v>
+        <v>-15.10469542997403</v>
       </c>
       <c r="F57">
-        <v>0.5004282523667198</v>
+        <v>-0.1612947576931753</v>
       </c>
       <c r="G57">
-        <v>-4.248861233226232</v>
+        <v>-4.265877437298086</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.13065814699716</v>
       </c>
       <c r="E58">
-        <v>-13.51729773674728</v>
+        <v>-15.09081112866651</v>
       </c>
       <c r="F58">
-        <v>0.4343378289565585</v>
+        <v>-0.3557714685502663</v>
       </c>
       <c r="G58">
-        <v>-4.698002946539154</v>
+        <v>-5.418337929338093</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.52494325371312</v>
       </c>
       <c r="E59">
-        <v>-13.39218505686337</v>
+        <v>-13.57185226311769</v>
       </c>
       <c r="F59">
-        <v>0.815263445385378</v>
+        <v>-0.3840754606710001</v>
       </c>
       <c r="G59">
-        <v>-5.238168109454337</v>
+        <v>-6.224538531789109</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.85178580250436</v>
       </c>
       <c r="E60">
-        <v>-12.85411630374598</v>
+        <v>-13.38767922522573</v>
       </c>
       <c r="F60">
-        <v>0.3351028162951228</v>
+        <v>-0.5501159399634181</v>
       </c>
       <c r="G60">
-        <v>-5.401560084545067</v>
+        <v>-6.118134287611394</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-15.11585162528906</v>
       </c>
       <c r="E61">
-        <v>-12.7296738380152</v>
+        <v>-13.76387767493894</v>
       </c>
       <c r="F61">
-        <v>0.50214023846131</v>
+        <v>-0.4816816317984065</v>
       </c>
       <c r="G61">
-        <v>-5.126384228775306</v>
+        <v>-5.605466515945396</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-15.32685295052997</v>
       </c>
       <c r="E62">
-        <v>-12.48002359444634</v>
+        <v>-14.13890777835817</v>
       </c>
       <c r="F62">
-        <v>0.5636980955414835</v>
+        <v>-0.1214487168607188</v>
       </c>
       <c r="G62">
-        <v>-5.202559881633936</v>
+        <v>-5.663477205430046</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-15.48188940497962</v>
       </c>
       <c r="E63">
-        <v>-11.75297256404086</v>
+        <v>-13.31838451596036</v>
       </c>
       <c r="F63">
-        <v>0.2223081135856945</v>
+        <v>-0.3279251674390945</v>
       </c>
       <c r="G63">
-        <v>-5.45436990698752</v>
+        <v>-6.826544685377878</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-15.5912317638715</v>
       </c>
       <c r="E64">
-        <v>-11.74881089642781</v>
+        <v>-13.14359900468631</v>
       </c>
       <c r="F64">
-        <v>0.425244981443063</v>
+        <v>-0.7359669965520681</v>
       </c>
       <c r="G64">
-        <v>-5.989996311968363</v>
+        <v>-7.134683643082162</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-15.66204918408769</v>
       </c>
       <c r="E65">
-        <v>-11.58412388219086</v>
+        <v>-13.07051396267652</v>
       </c>
       <c r="F65">
-        <v>0.1866208844871819</v>
+        <v>-0.8131188139286163</v>
       </c>
       <c r="G65">
-        <v>-6.003771491957271</v>
+        <v>-6.411872372219848</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-15.68860050064637</v>
       </c>
       <c r="E66">
-        <v>-12.02886078601016</v>
+        <v>-12.6381080935801</v>
       </c>
       <c r="F66">
-        <v>0.3747904865360354</v>
+        <v>-0.1612876310165559</v>
       </c>
       <c r="G66">
-        <v>-6.406171612801223</v>
+        <v>-6.516935845454157</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-15.68225248218562</v>
       </c>
       <c r="E67">
-        <v>-11.29347283495655</v>
+        <v>-13.1636692014883</v>
       </c>
       <c r="F67">
-        <v>0.01933402863931312</v>
+        <v>-0.3847556623616813</v>
       </c>
       <c r="G67">
-        <v>-6.545389984364194</v>
+        <v>-7.318859223068436</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-15.64546185127997</v>
       </c>
       <c r="E68">
-        <v>-11.64799347959504</v>
+        <v>-12.93959577911477</v>
       </c>
       <c r="F68">
-        <v>-0.3290242593444095</v>
+        <v>-0.8409975810110546</v>
       </c>
       <c r="G68">
-        <v>-6.240561572199182</v>
+        <v>-5.85146653387756</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-15.57132027352505</v>
       </c>
       <c r="E69">
-        <v>-11.84073439030951</v>
+        <v>-12.10279718113339</v>
       </c>
       <c r="F69">
-        <v>-0.09221667307353752</v>
+        <v>-1.151209936462545</v>
       </c>
       <c r="G69">
-        <v>-6.565703491793162</v>
+        <v>-6.347614683302594</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.47143112841116</v>
       </c>
       <c r="E70">
-        <v>-10.83550825856085</v>
+        <v>-12.49067909378639</v>
       </c>
       <c r="F70">
-        <v>-0.207367138332182</v>
+        <v>-0.8048716653739654</v>
       </c>
       <c r="G70">
-        <v>-6.830173043288919</v>
+        <v>-6.506669843736878</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.34637882165338</v>
       </c>
       <c r="E71">
-        <v>-11.89004041530502</v>
+        <v>-11.97222316159622</v>
       </c>
       <c r="F71">
-        <v>-0.3882706976409992</v>
+        <v>-0.9779129166655834</v>
       </c>
       <c r="G71">
-        <v>-7.172066323311611</v>
+        <v>-7.183868418159113</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.19314584528624</v>
       </c>
       <c r="E72">
-        <v>-11.99835245662048</v>
+        <v>-12.32290818875022</v>
       </c>
       <c r="F72">
-        <v>-0.2524512864799545</v>
+        <v>-1.0180574860631</v>
       </c>
       <c r="G72">
-        <v>-6.492560298648504</v>
+        <v>-7.52838033970337</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.02496302716969</v>
       </c>
       <c r="E73">
-        <v>-11.56717833245416</v>
+        <v>-13.1652043541769</v>
       </c>
       <c r="F73">
-        <v>-0.5356931301915111</v>
+        <v>-1.345360403901055</v>
       </c>
       <c r="G73">
-        <v>-6.128632027516423</v>
+        <v>-6.883095424279708</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.8402095470738</v>
       </c>
       <c r="E74">
-        <v>-10.86790496161172</v>
+        <v>-11.42614806643328</v>
       </c>
       <c r="F74">
-        <v>-0.4418110435242606</v>
+        <v>-1.471813778278191</v>
       </c>
       <c r="G74">
-        <v>-6.43639027248369</v>
+        <v>-7.178200764195881</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.64115001491847</v>
       </c>
       <c r="E75">
-        <v>-12.75658203056878</v>
+        <v>-13.15657308271828</v>
       </c>
       <c r="F75">
-        <v>-0.7854000011436373</v>
+        <v>-1.200806854616362</v>
       </c>
       <c r="G75">
-        <v>-6.422300590668552</v>
+        <v>-5.960774126493217</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.43939627501378</v>
       </c>
       <c r="E76">
-        <v>-12.12464253974639</v>
+        <v>-13.50607617815627</v>
       </c>
       <c r="F76">
-        <v>-0.396874180026624</v>
+        <v>-1.262641860231738</v>
       </c>
       <c r="G76">
-        <v>-5.99977897403691</v>
+        <v>-7.519815958393275</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.23122696538857</v>
       </c>
       <c r="E77">
-        <v>-11.62461749676745</v>
+        <v>-13.29004985409437</v>
       </c>
       <c r="F77">
-        <v>-0.8387352571108493</v>
+        <v>-1.264932690838421</v>
       </c>
       <c r="G77">
-        <v>-6.548068215705464</v>
+        <v>-6.39523688088501</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-14.02288402228462</v>
       </c>
       <c r="E78">
-        <v>-12.52261842096249</v>
+        <v>-14.42059244705729</v>
       </c>
       <c r="F78">
-        <v>-0.5392612196189961</v>
+        <v>-1.389982109921519</v>
       </c>
       <c r="G78">
-        <v>-5.979902458619125</v>
+        <v>-7.019138982670518</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-13.82121111428367</v>
       </c>
       <c r="E79">
-        <v>-13.28562553498887</v>
+        <v>-14.71832602763959</v>
       </c>
       <c r="F79">
-        <v>-0.636438998296276</v>
+        <v>-1.335478078988713</v>
       </c>
       <c r="G79">
-        <v>-5.849702013105128</v>
+        <v>-6.261838448380077</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.61716889046113</v>
       </c>
       <c r="E80">
-        <v>-14.09086066913679</v>
+        <v>-14.16367853118012</v>
       </c>
       <c r="F80">
-        <v>-0.8905778702527596</v>
+        <v>-1.63765946174301</v>
       </c>
       <c r="G80">
-        <v>-5.746972474476005</v>
+        <v>-6.428620422103021</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.41740123155972</v>
       </c>
       <c r="E81">
-        <v>-14.99103526085551</v>
+        <v>-15.73442502548066</v>
       </c>
       <c r="F81">
-        <v>-0.7956552887990654</v>
+        <v>-1.353906872873724</v>
       </c>
       <c r="G81">
-        <v>-5.2938448643338</v>
+        <v>-6.793975538362528</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-13.22231792573171</v>
       </c>
       <c r="E82">
-        <v>-16.25278133124266</v>
+        <v>-18.38511294418242</v>
       </c>
       <c r="F82">
-        <v>-1.168173010522817</v>
+        <v>-1.586885850094021</v>
       </c>
       <c r="G82">
-        <v>-5.541758377587662</v>
+        <v>-5.87426957155206</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.02182138966695</v>
       </c>
       <c r="E83">
-        <v>-14.71659615056866</v>
+        <v>-16.42470031846986</v>
       </c>
       <c r="F83">
-        <v>-1.05907626112594</v>
+        <v>-1.786982341392049</v>
       </c>
       <c r="G83">
-        <v>-5.137693052337457</v>
+        <v>-6.292017381516073</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-12.82291154300907</v>
       </c>
       <c r="E84">
-        <v>-16.00742860950708</v>
+        <v>-17.92043716930734</v>
       </c>
       <c r="F84">
-        <v>-1.009911694687037</v>
+        <v>-1.445144170662191</v>
       </c>
       <c r="G84">
-        <v>-5.273806132184592</v>
+        <v>-5.785825036924892</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-12.62330324522471</v>
       </c>
       <c r="E85">
-        <v>-17.82932427227302</v>
+        <v>-17.9866525162475</v>
       </c>
       <c r="F85">
-        <v>-1.193973955444199</v>
+        <v>-1.577969585790097</v>
       </c>
       <c r="G85">
-        <v>-4.992154849340017</v>
+        <v>-6.358652042130524</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-12.41470641902406</v>
       </c>
       <c r="E86">
-        <v>-18.69881392411576</v>
+        <v>-19.79399366355279</v>
       </c>
       <c r="F86">
-        <v>-1.163645195310576</v>
+        <v>-1.93132842520182</v>
       </c>
       <c r="G86">
-        <v>-5.073826007793837</v>
+        <v>-5.200523896127285</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.20483382201771</v>
       </c>
       <c r="E87">
-        <v>-20.34919363384119</v>
+        <v>-20.82666234778793</v>
       </c>
       <c r="F87">
-        <v>-1.439225861656194</v>
+        <v>-1.876034125017209</v>
       </c>
       <c r="G87">
-        <v>-4.62393611118904</v>
+        <v>-4.604105943408805</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.98820853073375</v>
       </c>
       <c r="E88">
-        <v>-20.89486569481745</v>
+        <v>-22.03282592820494</v>
       </c>
       <c r="F88">
-        <v>-1.297835764937591</v>
+        <v>-1.895445608422751</v>
       </c>
       <c r="G88">
-        <v>-4.312062858116458</v>
+        <v>-4.81562331900392</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.75988400651982</v>
       </c>
       <c r="E89">
-        <v>-22.80011245016857</v>
+        <v>-23.49047831263792</v>
       </c>
       <c r="F89">
-        <v>-1.172696074617312</v>
+        <v>-1.859196163724257</v>
       </c>
       <c r="G89">
-        <v>-4.647258904513206</v>
+        <v>-5.224111533094592</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.52342690145065</v>
       </c>
       <c r="E90">
-        <v>-24.78063150047518</v>
+        <v>-25.56070643303648</v>
       </c>
       <c r="F90">
-        <v>-1.134027519132985</v>
+        <v>-1.420849330066392</v>
       </c>
       <c r="G90">
-        <v>-4.917882760166468</v>
+        <v>-4.974665237256047</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.26929248194351</v>
       </c>
       <c r="E91">
-        <v>-26.00901630284783</v>
+        <v>-27.36663922492538</v>
       </c>
       <c r="F91">
-        <v>-1.463293440453127</v>
+        <v>-1.721445423199334</v>
       </c>
       <c r="G91">
-        <v>-4.931988994709302</v>
+        <v>-4.251347452926225</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.99369445373554</v>
       </c>
       <c r="E92">
-        <v>-27.69456867019083</v>
+        <v>-28.3723136756008</v>
       </c>
       <c r="F92">
-        <v>-1.241126423517535</v>
+        <v>-1.556182543511397</v>
       </c>
       <c r="G92">
-        <v>-4.94585355942777</v>
+        <v>-5.768994223403237</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.69727462764324</v>
       </c>
       <c r="E93">
-        <v>-29.19409132529873</v>
+        <v>-30.35438372825504</v>
       </c>
       <c r="F93">
-        <v>-1.550063103854139</v>
+        <v>-1.992286057740042</v>
       </c>
       <c r="G93">
-        <v>-4.333882663765794</v>
+        <v>-5.38642095979398</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.37073126201542</v>
       </c>
       <c r="E94">
-        <v>-32.10437401649018</v>
+        <v>-31.90438528312644</v>
       </c>
       <c r="F94">
-        <v>-1.490823000381211</v>
+        <v>-1.467898857255225</v>
       </c>
       <c r="G94">
-        <v>-5.157460319752445</v>
+        <v>-5.771851224203627</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.01902099983972</v>
       </c>
       <c r="E95">
-        <v>-34.0570837079157</v>
+        <v>-34.33873441305976</v>
       </c>
       <c r="F95">
-        <v>-1.367306608624258</v>
+        <v>-1.450821756369041</v>
       </c>
       <c r="G95">
-        <v>-4.350087784180527</v>
+        <v>-5.118223734021003</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.648619566032451</v>
       </c>
       <c r="E96">
-        <v>-37.13081034722899</v>
+        <v>-37.33753292144215</v>
       </c>
       <c r="F96">
-        <v>-1.358632651325396</v>
+        <v>-1.2906512830522</v>
       </c>
       <c r="G96">
-        <v>-4.514525891661666</v>
+        <v>-5.831351659180949</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.261191591796507</v>
       </c>
       <c r="E97">
-        <v>-38.65019262509754</v>
+        <v>-38.54696832432969</v>
       </c>
       <c r="F97">
-        <v>-1.230620910327467</v>
+        <v>-1.790396019492779</v>
       </c>
       <c r="G97">
-        <v>-5.268009366945328</v>
+        <v>-5.95757613950228</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.875586694214569</v>
       </c>
       <c r="E98">
-        <v>-41.49071643843783</v>
+        <v>-40.29869075387277</v>
       </c>
       <c r="F98">
-        <v>-1.630185953528051</v>
+        <v>-1.640149047442081</v>
       </c>
       <c r="G98">
-        <v>-5.490491269366508</v>
+        <v>-5.982418473228972</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.507984135196137</v>
       </c>
       <c r="E99">
-        <v>-43.44982939211019</v>
+        <v>-42.88696724380081</v>
       </c>
       <c r="F99">
-        <v>-1.518229823100848</v>
+        <v>-1.466831439468219</v>
       </c>
       <c r="G99">
-        <v>-5.850662071311517</v>
+        <v>-5.584845127781277</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.170865344489419</v>
       </c>
       <c r="E100">
-        <v>-46.26832670787718</v>
+        <v>-44.30411469247218</v>
       </c>
       <c r="F100">
-        <v>-1.319610137568968</v>
+        <v>-1.543146268268457</v>
       </c>
       <c r="G100">
-        <v>-5.36883865243491</v>
+        <v>-6.441624244981278</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.88862764867221</v>
       </c>
       <c r="E101">
-        <v>-48.09833739606486</v>
+        <v>-48.70481554177912</v>
       </c>
       <c r="F101">
-        <v>-1.387550329488362</v>
+        <v>-1.60522516459481</v>
       </c>
       <c r="G101">
-        <v>-5.32550692187139</v>
+        <v>-6.031358267936017</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.675604351308521</v>
       </c>
       <c r="E102">
-        <v>-49.95093724472131</v>
+        <v>-50.23829043075953</v>
       </c>
       <c r="F102">
-        <v>-1.474756303869078</v>
+        <v>-1.194395221217706</v>
       </c>
       <c r="G102">
-        <v>-5.829772528958716</v>
+        <v>-6.157516537346564</v>
       </c>
     </row>
   </sheetData>
